--- a/Received_data/Statistics/all_descriptors_без_выбросов.xlsx
+++ b/Received_data/Statistics/all_descriptors_без_выбросов.xlsx
@@ -578,13 +578,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.0173933983860999</v>
+        <v>0.2690309998190661</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2322797547700177</v>
+        <v>0.2877387092958209</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0245906947149354</v>
+        <v>0.240345119579827</v>
       </c>
       <c r="M2" t="n">
         <v>5.352301132186443</v>
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.004472713195976</v>
+        <v>0.0465805653459565</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0531708509965983</v>
+        <v>0.0796123181345106</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0053902627855156</v>
+        <v>0.0783126025346277</v>
       </c>
       <c r="M3" t="n">
         <v>2.58374935445008</v>
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.0249591233654078</v>
+        <v>0.4506534192646358</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3862090824266627</v>
+        <v>0.4655637766476879</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0375834562175953</v>
+        <v>0.3231232408160088</v>
       </c>
       <c r="M4" t="n">
         <v>5.654826975821345</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.0322927743614181</v>
+        <v>0.5160183137743313</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3848551224529898</v>
+        <v>0.4372897970165201</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0569148147217572</v>
+        <v>0.4532330121509276</v>
       </c>
       <c r="M5" t="n">
         <v>5.709992170112354</v>
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.0270244413884244</v>
+        <v>0.4951425564878134</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4410258460726654</v>
+        <v>0.5440802715127648</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0398048922390223</v>
+        <v>0.3518767583635966</v>
       </c>
       <c r="M6" t="n">
         <v>5.079193721871124</v>
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.0396712082248952</v>
+        <v>0.7509123471241711</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6240732067962905</v>
+        <v>0.7346656750451671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.064438476545862</v>
+        <v>0.5108142663816629</v>
       </c>
       <c r="M7" t="n">
         <v>5.632450874857552</v>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.0217302615219645</v>
+        <v>0.408816579681</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3394663308882283</v>
+        <v>0.4088769052069654</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0558444588660922</v>
+        <v>0.4300863440582981</v>
       </c>
       <c r="M8" t="n">
         <v>2.60865750219362</v>
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.0258674021163818</v>
+        <v>0.6418448299863009</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5097644843550693</v>
+        <v>0.5641086288591435</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0552019712062638</v>
+        <v>0.3206501064324983</v>
       </c>
       <c r="M9" t="n">
         <v>4.01600240250546</v>
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.0244308737980026</v>
+        <v>0.6088565298164966</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4747079021204688</v>
+        <v>0.5156206064741174</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0568354602731157</v>
+        <v>0.3307398229002759</v>
       </c>
       <c r="M10" t="n">
         <v>3.652519893899194</v>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.0221950393088321</v>
+        <v>0.7003131761883381</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6348389779404778</v>
+        <v>0.7560547452982561</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0588119041810382</v>
+        <v>0.3317449852069584</v>
       </c>
       <c r="M11" t="n">
         <v>3.889694006722238</v>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.0182186861199509</v>
+        <v>0.2375731173886264</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1365909551061646</v>
+        <v>0.1314653548916373</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0374814002207315</v>
+        <v>0.2957013714955175</v>
       </c>
       <c r="M12" t="n">
         <v>4.020827516891005</v>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.021704371217226</v>
+        <v>0.2548943548179891</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1306649662120857</v>
+        <v>0.1158458948997201</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0426217316241915</v>
+        <v>0.3448743402690822</v>
       </c>
       <c r="M13" t="n">
         <v>2.644139210658552</v>
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.0266733322983177</v>
+        <v>0.7118025515651388</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5384094499992657</v>
+        <v>0.5668148464850952</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06789452298340461</v>
+        <v>0.361870768411184</v>
       </c>
       <c r="M14" t="n">
         <v>3.545527383197837</v>
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.0169434044048361</v>
+        <v>0.5118259787711913</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3948341701481413</v>
+        <v>0.4182937328920724</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0487446917575044</v>
+        <v>0.2438525990667204</v>
       </c>
       <c r="M15" t="n">
         <v>3.108426625970293</v>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.0217954412227886</v>
+        <v>0.4105861364840265</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2769428814739353</v>
+        <v>0.2795891257691155</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0487086043862537</v>
+        <v>0.3195066790746462</v>
       </c>
       <c r="M16" t="n">
         <v>3.573559544299648</v>
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.0197190934402101</v>
+        <v>0.3882038793270921</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2763994220738517</v>
+        <v>0.2885509954520376</v>
       </c>
       <c r="L17" t="n">
-        <v>0.042059659344565</v>
+        <v>0.2818557074885343</v>
       </c>
       <c r="M17" t="n">
         <v>3.387313625786463</v>
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.0275871116693442</v>
+        <v>0.6192108295112904</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4920351116614289</v>
+        <v>0.5509416741443253</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0558267412723844</v>
+        <v>0.3682366991474657</v>
       </c>
       <c r="M18" t="n">
         <v>3.439523695793105</v>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.0204465908424383</v>
+        <v>0.4738498240126729</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3905573401463839</v>
+        <v>0.4534177904379865</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0468428432024748</v>
+        <v>0.3051241520880961</v>
       </c>
       <c r="M19" t="n">
         <v>3.655503139741952</v>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.0210163972281181</v>
+        <v>0.4997393031156912</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3860762709282901</v>
+        <v>0.418988609237074</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0471373842803803</v>
+        <v>0.283480905468239</v>
       </c>
       <c r="M20" t="n">
         <v>3.368894817961628</v>
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.01698307867009</v>
+        <v>0.5073563595041009</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3756817841715514</v>
+        <v>0.380972410991964</v>
       </c>
       <c r="L21" t="n">
-        <v>0.047827752217476</v>
+        <v>0.2296533461893642</v>
       </c>
       <c r="M21" t="n">
         <v>3.490068239274634</v>
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.009399943216990199</v>
+        <v>0.2025732628674068</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1650149616130282</v>
+        <v>0.1887481526802946</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0195626777713561</v>
+        <v>0.1394486885275351</v>
       </c>
       <c r="M22" t="n">
         <v>3.882969252893256</v>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.0116450947133806</v>
+        <v>0.3381957979817199</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2895629355318336</v>
+        <v>0.3334180276690111</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0278370892966118</v>
+        <v>0.1592205310207436</v>
       </c>
       <c r="M23" t="n">
         <v>3.20987438106004</v>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.0147358356256163</v>
+        <v>0.3659374547720501</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3084085114523521</v>
+        <v>0.3537791547118687</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0310174318412598</v>
+        <v>0.2008533700965059</v>
       </c>
       <c r="M24" t="n">
         <v>4.070520171629594</v>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.0208620969227272</v>
+        <v>0.4804720809977034</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3824988359009866</v>
+        <v>0.4240412499557642</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0420364630681176</v>
+        <v>0.2725201081216919</v>
       </c>
       <c r="M25" t="n">
         <v>3.564435499577995</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.0157476066446719</v>
+        <v>0.3551694333839713</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2847998613376867</v>
+        <v>0.3176789124307519</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0320885713129957</v>
+        <v>0.215495564936142</v>
       </c>
       <c r="M26" t="n">
         <v>3.410707086995083</v>
@@ -2628,13 +2628,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.0218613344777962</v>
+        <v>0.3526706994371589</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2509685112308539</v>
+        <v>0.271441478577443</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0399648728970922</v>
+        <v>0.3119288977180103</v>
       </c>
       <c r="M27" t="n">
         <v>3.886104462902997</v>
@@ -2710,13 +2710,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.0208253088929616</v>
+        <v>0.4201911696708275</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3332264518917202</v>
+        <v>0.3757337953737621</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0388253200371644</v>
+        <v>0.2819610587088148</v>
       </c>
       <c r="M28" t="n">
         <v>3.730404099806767</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.015692123993842</v>
+        <v>0.3657893860165851</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3086242596195027</v>
+        <v>0.3575593946704997</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0308668983875977</v>
+        <v>0.2097190254525995</v>
       </c>
       <c r="M29" t="n">
         <v>3.79488196372292</v>
@@ -2874,13 +2874,13 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.0104419459296858</v>
+        <v>0.2385623987284484</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2318059224551034</v>
+        <v>0.2949927916422398</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0194244820373197</v>
+        <v>0.159536738746196</v>
       </c>
       <c r="M30" t="n">
         <v>3.7659661182741</v>
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.009951458176707799</v>
+        <v>0.1010739889381716</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0823019235267707</v>
+        <v>0.1076739269798482</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0125753832183831</v>
+        <v>0.1506720846111289</v>
       </c>
       <c r="M31" t="n">
         <v>4.395719295945483</v>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.0184539599677239</v>
+        <v>0.4031379944252481</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3132097845783732</v>
+        <v>0.343690268814311</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0342524475353541</v>
+        <v>0.2206169774600891</v>
       </c>
       <c r="M32" t="n">
         <v>4.619340620351844</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.0194933171580599</v>
+        <v>0.3930966092089683</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3055141597255985</v>
+        <v>0.3384508036631666</v>
       </c>
       <c r="L33" t="n">
-        <v>0.033987649699597</v>
+        <v>0.2375257966085014</v>
       </c>
       <c r="M33" t="n">
         <v>3.974852122176501</v>
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.0135129852834182</v>
+        <v>0.2274190232038442</v>
       </c>
       <c r="K34" t="n">
-        <v>0.180461233515196</v>
+        <v>0.2096064915703442</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0217853271235439</v>
+        <v>0.1812513263630182</v>
       </c>
       <c r="M34" t="n">
         <v>3.573171171821408</v>
@@ -3284,13 +3284,13 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.0211218317760266</v>
+        <v>0.3331854550165337</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2491042078760043</v>
+        <v>0.2794278849239734</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0351429699857023</v>
+        <v>0.296018750778193</v>
       </c>
       <c r="M35" t="n">
         <v>3.875550712966066</v>
@@ -3366,13 +3366,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.0161008671441829</v>
+        <v>0.298138634988658</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2209598574236544</v>
+        <v>0.2398123737050207</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0280911134461554</v>
+        <v>0.2038916432542536</v>
       </c>
       <c r="M36" t="n">
         <v>3.594196446638886</v>
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.0134199122236733</v>
+        <v>0.19550732040338</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1468905399819972</v>
+        <v>0.1684672317660525</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0204879377517367</v>
+        <v>0.1841363005234351</v>
       </c>
       <c r="M37" t="n">
         <v>3.679439122587873</v>
@@ -3530,13 +3530,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.0185496821222094</v>
+        <v>0.2987733230664052</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2284483254569995</v>
+        <v>0.2595959640834542</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0298423607750997</v>
+        <v>0.2518802160407233</v>
       </c>
       <c r="M38" t="n">
         <v>2.536245799327885</v>
@@ -3612,13 +3612,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.0274976733571641</v>
+        <v>0.7233054527021907</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5620662564837872</v>
+        <v>0.5998688397650174</v>
       </c>
       <c r="L39" t="n">
-        <v>0.057825737030262</v>
+        <v>0.3056754219848887</v>
       </c>
       <c r="M39" t="n">
         <v>4.835084951715005</v>
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.0333571265975992</v>
+        <v>0.7070879845652649</v>
       </c>
       <c r="K40" t="n">
-        <v>0.4948861850334256</v>
+        <v>0.499184858137055</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0688846323917018</v>
+        <v>0.4141551736846321</v>
       </c>
       <c r="M40" t="n">
         <v>5.087023204294344</v>
@@ -3776,13 +3776,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.02388500517134</v>
+        <v>0.4088719300152404</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2643744889032274</v>
+        <v>0.2566417227815694</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0441289737246278</v>
+        <v>0.3073954913338668</v>
       </c>
       <c r="M41" t="n">
         <v>4.522610621859644</v>
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.0311338877171607</v>
+        <v>0.6203541397610203</v>
       </c>
       <c r="K42" t="n">
-        <v>0.4523364796309452</v>
+        <v>0.4761895573237514</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0564716806345182</v>
+        <v>0.3783518545693964</v>
       </c>
       <c r="M42" t="n">
         <v>4.524178173204748</v>
@@ -3940,13 +3940,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0.0234678629527612</v>
+        <v>0.399148185590241</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2698040106392687</v>
+        <v>0.27599676840242</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0439740436257434</v>
+        <v>0.3153281810365074</v>
       </c>
       <c r="M43" t="n">
         <v>4.672207189795118</v>
@@ -4022,13 +4022,13 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0.0273928425185539</v>
+        <v>0.5987422017360995</v>
       </c>
       <c r="K44" t="n">
-        <v>0.4551862605788104</v>
+        <v>0.4917292290303663</v>
       </c>
       <c r="L44" t="n">
-        <v>0.055597557393304</v>
+        <v>0.3513735851743547</v>
       </c>
       <c r="M44" t="n">
         <v>4.211369118544574</v>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0.031742246965116</v>
+        <v>0.8053737073053983</v>
       </c>
       <c r="K45" t="n">
-        <v>0.6295975128947925</v>
+        <v>0.6799064121821774</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0682785772955239</v>
+        <v>0.3851211805538757</v>
       </c>
       <c r="M45" t="n">
         <v>4.365313025165403</v>
@@ -4186,13 +4186,13 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0.0192443201477153</v>
+        <v>0.5327040297731667</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4355291627069031</v>
+        <v>0.481864795129911</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0402098154031005</v>
+        <v>0.2154393433162701</v>
       </c>
       <c r="M46" t="n">
         <v>5.01979598020402</v>
@@ -4268,13 +4268,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0.0257978614672374</v>
+        <v>0.5999508187500366</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5015996878036322</v>
+        <v>0.5740776450533489</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0436134487717011</v>
+        <v>0.2846691339882186</v>
       </c>
       <c r="M47" t="n">
         <v>4.462366177231737</v>
@@ -4350,13 +4350,13 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0.0241588007066897</v>
+        <v>0.493475409830412</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4084896418455614</v>
+        <v>0.4777674165943287</v>
       </c>
       <c r="L48" t="n">
-        <v>0.0517490014469498</v>
+        <v>0.383882906466264</v>
       </c>
       <c r="M48" t="n">
         <v>4.192342472999029</v>
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0.0180269085638338</v>
+        <v>0.4037158913143123</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3332568836465125</v>
+        <v>0.3828084568031961</v>
       </c>
       <c r="L49" t="n">
-        <v>0.0342937522011095</v>
+        <v>0.2308356778696913</v>
       </c>
       <c r="M49" t="n">
         <v>3.905427694181535</v>
@@ -4514,13 +4514,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0.0232297359046819</v>
+        <v>0.415836703921175</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3319903972435857</v>
+        <v>0.3874931695315969</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0470783207442685</v>
+        <v>0.3704112799995191</v>
       </c>
       <c r="M50" t="n">
         <v>3.439537771790611</v>
@@ -4596,13 +4596,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0.0168543473379848</v>
+        <v>0.2685516855279293</v>
       </c>
       <c r="K51" t="n">
-        <v>0.2280403481368523</v>
+        <v>0.28077401524462</v>
       </c>
       <c r="L51" t="n">
-        <v>0.0272365012811265</v>
+        <v>0.2485629206329518</v>
       </c>
       <c r="M51" t="n">
         <v>3.251533226917577</v>
@@ -4678,13 +4678,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0.0246492303996124</v>
+        <v>0.4293498700368615</v>
       </c>
       <c r="K52" t="n">
-        <v>0.3453656570817986</v>
+        <v>0.4053162224229094</v>
       </c>
       <c r="L52" t="n">
-        <v>0.0464021045395159</v>
+        <v>0.3754168524029217</v>
       </c>
       <c r="M52" t="n">
         <v>4.062709612098968</v>
@@ -4760,13 +4760,13 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>0.024123293987953</v>
+        <v>0.5044191004324514</v>
       </c>
       <c r="K53" t="n">
-        <v>0.38994850528159</v>
+        <v>0.434524880255021</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0571429058845744</v>
+        <v>0.3914592767826597</v>
       </c>
       <c r="M53" t="n">
         <v>3.0605531204667</v>
@@ -4842,13 +4842,13 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>0.0256992040115794</v>
+        <v>0.5776169247182797</v>
       </c>
       <c r="K54" t="n">
-        <v>0.4350089934593216</v>
+        <v>0.4626387840513375</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0516612153422641</v>
+        <v>0.3177460883933316</v>
       </c>
       <c r="M54" t="n">
         <v>4.478929629713404</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>0.0159335664507775</v>
+        <v>0.4503463499817454</v>
       </c>
       <c r="K55" t="n">
-        <v>0.36930714732731</v>
+        <v>0.4111657131773347</v>
       </c>
       <c r="L55" t="n">
-        <v>0.0372533225973458</v>
+        <v>0.2019717401053701</v>
       </c>
       <c r="M55" t="n">
         <v>4.406514920961255</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>0.0175754748557132</v>
+        <v>0.3733446067738971</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3141789213381668</v>
+        <v>0.3679720229130154</v>
       </c>
       <c r="L56" t="n">
-        <v>0.0327956388165273</v>
+        <v>0.2352655624172282</v>
       </c>
       <c r="M56" t="n">
         <v>4.60077946284845</v>
@@ -5088,13 +5088,13 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>0.0235220942467185</v>
+        <v>0.149497359939904</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1291198077505526</v>
+        <v>0.2046208077635786</v>
       </c>
       <c r="L57" t="n">
-        <v>0.0463798400525287</v>
+        <v>0.5281236719554763</v>
       </c>
       <c r="M57" t="n">
         <v>4.84437951714597</v>
@@ -5170,13 +5170,13 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0.018730836594441</v>
+        <v>0.2854209055865511</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1829876901253901</v>
+        <v>0.1832357661868913</v>
       </c>
       <c r="L58" t="n">
-        <v>0.0349515895070512</v>
+        <v>0.2660082640525374</v>
       </c>
       <c r="M58" t="n">
         <v>4.863820589029987</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>0.0153215627679824</v>
+        <v>0.1853622769513438</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1658354530936368</v>
+        <v>0.2194982094208072</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0205234188458995</v>
+        <v>0.2341058872253786</v>
       </c>
       <c r="M59" t="n">
         <v>4.403650902204272</v>
@@ -5334,13 +5334,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0.0116691817839194</v>
+        <v>0.1410569122035689</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1272611300298418</v>
+        <v>0.1698984361700866</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0167795886674976</v>
+        <v>0.185434595039515</v>
       </c>
       <c r="M60" t="n">
         <v>5.22514512454999</v>
@@ -5416,13 +5416,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>0.0142575107356747</v>
+        <v>0.1703352000429601</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1498382993273038</v>
+        <v>0.1967735494826967</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0188673621396177</v>
+        <v>0.2155482803899977</v>
       </c>
       <c r="M61" t="n">
         <v>4.239311319273658</v>
@@ -5498,13 +5498,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.0118786925230344</v>
+        <v>0.1639603117254342</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1458549662612587</v>
+        <v>0.1885992288361103</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0177008731008839</v>
+        <v>0.1816646238159471</v>
       </c>
       <c r="M62" t="n">
         <v>4.257106636110972</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0.0138168076001099</v>
+        <v>0.1771152374867095</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1591705564285521</v>
+        <v>0.2100732795285566</v>
       </c>
       <c r="L63" t="n">
-        <v>0.0200248853674659</v>
+        <v>0.2166095627178051</v>
       </c>
       <c r="M63" t="n">
         <v>3.981113715776941</v>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.0056662958426229</v>
+        <v>0.0930893630232769</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0937435915509638</v>
+        <v>0.1270494458008654</v>
       </c>
       <c r="L64" t="n">
-        <v>0.008726655473890701</v>
+        <v>0.0912172230402596</v>
       </c>
       <c r="M64" t="n">
         <v>1.862389874674297</v>
@@ -5744,13 +5744,13 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0.0066783558086605</v>
+        <v>0.1250200387554153</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1218764519953435</v>
+        <v>0.1601695627310222</v>
       </c>
       <c r="L65" t="n">
-        <v>0.010943548354099</v>
+        <v>0.1015553877051306</v>
       </c>
       <c r="M65" t="n">
         <v>5.076505649196209</v>
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.0036405643022522</v>
+        <v>0.0310568930786714</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0376575062902274</v>
+        <v>0.0601142066719145</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0046519009848541</v>
+        <v>0.0703069956302507</v>
       </c>
       <c r="M66" t="n">
         <v>6.751163592335002</v>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.0019519428840177</v>
+        <v>0.0255378122637966</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0327628065193989</v>
+        <v>0.0500010978284005</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0035429071425772</v>
+        <v>0.0442469103383955</v>
       </c>
       <c r="M67" t="n">
         <v>2.173641521440373</v>
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0.0022529784977764</v>
+        <v>0.0289441985753136</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0366373742720183</v>
+        <v>0.0566835989911642</v>
       </c>
       <c r="L68" t="n">
-        <v>0.003908066207771</v>
+        <v>0.0485685421485773</v>
       </c>
       <c r="M68" t="n">
         <v>4.47684453156095</v>
@@ -6072,13 +6072,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0.0146576731864006</v>
+        <v>0.250588190260506</v>
       </c>
       <c r="K69" t="n">
-        <v>0.2047672306068312</v>
+        <v>0.2432260452980393</v>
       </c>
       <c r="L69" t="n">
-        <v>0.0267896138958232</v>
+        <v>0.2258117677198498</v>
       </c>
       <c r="M69" t="n">
         <v>3.02731240320993</v>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0.002941912729526</v>
+        <v>0.0453986503499962</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0477333992703427</v>
+        <v>0.06615831058224619</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0053032855605625</v>
+        <v>0.0565662681756886</v>
       </c>
       <c r="M70" t="n">
         <v>3.753665951214149</v>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.0034100116557521</v>
+        <v>0.07358473802961191</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0722462187075799</v>
+        <v>0.09353426753557249</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0071105373537763</v>
+        <v>0.0593824578545125</v>
       </c>
       <c r="M71" t="n">
         <v>3.396979162382732</v>
@@ -6318,13 +6318,13 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.0049243196388706</v>
+        <v>0.0881213652832526</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0829136344004406</v>
+        <v>0.1081319400160554</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0083703541258847</v>
+        <v>0.0771155575409429</v>
       </c>
       <c r="M72" t="n">
         <v>4.589734136364382</v>
@@ -6400,13 +6400,13 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.021946828306971</v>
+        <v>0.2085389661966377</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1662208578512028</v>
+        <v>0.2253445997735045</v>
       </c>
       <c r="L73" t="n">
-        <v>0.0446552083376257</v>
+        <v>0.4563006706910122</v>
       </c>
       <c r="M73" t="n">
         <v>3.231576340957623</v>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.0160406045713445</v>
+        <v>0.3003002692915861</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2429224276590119</v>
+        <v>0.2815156770986922</v>
       </c>
       <c r="L74" t="n">
-        <v>0.0280421921575422</v>
+        <v>0.2180854078144034</v>
       </c>
       <c r="M74" t="n">
         <v>3.147013029582898</v>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0.0168547604869585</v>
+        <v>0.3323500108632941</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2723366590876263</v>
+        <v>0.3163440779111925</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0295655034236496</v>
+        <v>0.2225146379009981</v>
       </c>
       <c r="M75" t="n">
         <v>3.374348501935452</v>
@@ -6646,13 +6646,13 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.0160729752325103</v>
+        <v>0.2757055271756719</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2128272678061645</v>
+        <v>0.2414356895777341</v>
       </c>
       <c r="L76" t="n">
-        <v>0.0271467392561324</v>
+        <v>0.2180078960224756</v>
       </c>
       <c r="M76" t="n">
         <v>2.960062090557521</v>
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.0160098803009938</v>
+        <v>0.2549514538838975</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1884364303107679</v>
+        <v>0.2098768725670081</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0271811812030338</v>
+        <v>0.2237614138857671</v>
       </c>
       <c r="M77" t="n">
         <v>2.916158142678256</v>
@@ -6810,13 +6810,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.0148443973265603</v>
+        <v>0.2332360981518333</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1778443520452274</v>
+        <v>0.2028594066211463</v>
       </c>
       <c r="L78" t="n">
-        <v>0.02382099112181</v>
+        <v>0.2041975837173477</v>
       </c>
       <c r="M78" t="n">
         <v>3.201125766613463</v>
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.0160098803009938</v>
+        <v>0.2549514538838975</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1884364303107679</v>
+        <v>0.2098768725670081</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0271811812030338</v>
+        <v>0.2237614138857671</v>
       </c>
       <c r="M79" t="n">
         <v>3.136213782197314</v>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0.0167234750240851</v>
+        <v>0.2595021015000975</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1960756487740588</v>
+        <v>0.2222181262520525</v>
       </c>
       <c r="L80" t="n">
-        <v>0.0279278295469564</v>
+        <v>0.2411211425823762</v>
       </c>
       <c r="M80" t="n">
         <v>2.865785150783829</v>
@@ -7056,13 +7056,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.0182087790894275</v>
+        <v>0.3370904153865651</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2728376454262665</v>
+        <v>0.31693314803395</v>
       </c>
       <c r="L81" t="n">
-        <v>0.0329735694596549</v>
+        <v>0.2592937858772864</v>
       </c>
       <c r="M81" t="n">
         <v>3.020236607372143</v>
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>0.0193411335141742</v>
+        <v>0.4145689196800048</v>
       </c>
       <c r="K82" t="n">
-        <v>0.3152750718712355</v>
+        <v>0.3407989123339653</v>
       </c>
       <c r="L82" t="n">
-        <v>0.0380518855606162</v>
+        <v>0.2502841988091951</v>
       </c>
       <c r="M82" t="n">
         <v>2.939164264548782</v>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>0.0176792191160447</v>
+        <v>0.3895006712384356</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3233959589591641</v>
+        <v>0.3736311848160213</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0338673852554565</v>
+        <v>0.2351919588599153</v>
       </c>
       <c r="M83" t="n">
         <v>2.982550514170568</v>
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>0.003084445762933</v>
+        <v>0.06924042342008389</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0718995208304965</v>
+        <v>0.0951832753269642</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0057677055252928</v>
+        <v>0.0517844459478906</v>
       </c>
       <c r="M84" t="n">
         <v>2.632354732610656</v>
@@ -7384,13 +7384,13 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>0.0025633944965908</v>
+        <v>0.0598388599061929</v>
       </c>
       <c r="K85" t="n">
-        <v>0.06437784207879001</v>
+        <v>0.08687248838960709</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0052491276700824</v>
+        <v>0.0460364422422283</v>
       </c>
       <c r="M85" t="n">
         <v>3.271960250176574</v>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>0.001457688013135</v>
+        <v>0.0208271795040416</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0321114068760841</v>
+        <v>0.0509423906060261</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0022110764637704</v>
+        <v>0.0339231670722419</v>
       </c>
       <c r="M86" t="n">
         <v>3.185832710901545</v>
@@ -7548,13 +7548,13 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>0.0027135316404613</v>
+        <v>0.06256298154716031</v>
       </c>
       <c r="K87" t="n">
-        <v>0.06963188768146129</v>
+        <v>0.0958305414727689</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0052864245633104</v>
+        <v>0.0488646324024988</v>
       </c>
       <c r="M87" t="n">
         <v>3.903136613933175</v>
@@ -7630,13 +7630,13 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>0.0042522673599466</v>
+        <v>0.0715967368115405</v>
       </c>
       <c r="K88" t="n">
-        <v>0.07522045897001819</v>
+        <v>0.1035623886791977</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0068347486901416</v>
+        <v>0.0711617907462687</v>
       </c>
       <c r="M88" t="n">
         <v>4.963546536248648</v>
@@ -7712,13 +7712,13 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>0.0052874415065564</v>
+        <v>0.0667542996740885</v>
       </c>
       <c r="K89" t="n">
-        <v>0.069462196501049</v>
+        <v>0.09755709531223331</v>
       </c>
       <c r="L89" t="n">
-        <v>0.0064926756833727</v>
+        <v>0.0843721804913503</v>
       </c>
       <c r="M89" t="n">
         <v>4.730240402096238</v>
@@ -7794,13 +7794,13 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>0.002694983917617</v>
+        <v>0.0503427122558302</v>
       </c>
       <c r="K90" t="n">
-        <v>0.0577963712653913</v>
+        <v>0.08165227155081339</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0044507500362627</v>
+        <v>0.0482547480568968</v>
       </c>
       <c r="M90" t="n">
         <v>3.268252991107606</v>
@@ -7876,13 +7876,13 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>0.0074445070113968</v>
+        <v>0.08015918993714891</v>
       </c>
       <c r="K91" t="n">
-        <v>0.08207634968790629</v>
+        <v>0.1183474084414164</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0100125077147509</v>
+        <v>0.1292842418990987</v>
       </c>
       <c r="M91" t="n">
         <v>3.171393195282256</v>
@@ -7958,13 +7958,13 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>0.0082001007141843</v>
+        <v>0.0577811553559578</v>
       </c>
       <c r="K92" t="n">
-        <v>0.067323102547782</v>
+        <v>0.1106180703836583</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0119596010188655</v>
+        <v>0.1661325002046458</v>
       </c>
       <c r="M92" t="n">
         <v>5.758581639861432</v>
@@ -8040,13 +8040,13 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>0.0066742568721932</v>
+        <v>0.1258561381778225</v>
       </c>
       <c r="K93" t="n">
-        <v>0.116063769288506</v>
+        <v>0.1477258430508749</v>
       </c>
       <c r="L93" t="n">
-        <v>0.0116932052264143</v>
+        <v>0.1000797220583495</v>
       </c>
       <c r="M93" t="n">
         <v>4.599423801931846</v>
@@ -8122,13 +8122,13 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>0.0065021546755855</v>
+        <v>0.1029305899458807</v>
       </c>
       <c r="K94" t="n">
-        <v>0.0916909122621376</v>
+        <v>0.1162779815461913</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0100262504184733</v>
+        <v>0.0970102524793984</v>
       </c>
       <c r="M94" t="n">
         <v>5.412883507108889</v>
@@ -8204,13 +8204,13 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>0.0035393288484247</v>
+        <v>0.07453256902421609</v>
       </c>
       <c r="K95" t="n">
-        <v>0.07375158671126859</v>
+        <v>0.0954314586728383</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0061302318312063</v>
+        <v>0.0557138528186474</v>
       </c>
       <c r="M95" t="n">
         <v>5.368106440618767</v>
@@ -8286,13 +8286,13 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>0.0034353721597768</v>
+        <v>0.06818770650997941</v>
       </c>
       <c r="K96" t="n">
-        <v>0.0725769253042769</v>
+        <v>0.0989040569959081</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0062548295702911</v>
+        <v>0.0603953540486235</v>
       </c>
       <c r="M96" t="n">
         <v>3.846188236663951</v>

--- a/Received_data/Statistics/all_descriptors_без_выбросов.xlsx
+++ b/Received_data/Statistics/all_descriptors_без_выбросов.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X96"/>
+  <dimension ref="A1:X87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5631,30 +5631,30 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ADOM-SL8-1-2025</t>
+          <t>ADOM-SL9-1-2025</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.405625222222182</v>
+        <v>23.72320299999995</v>
       </c>
       <c r="D64" t="n">
-        <v>2.586780777777749</v>
+        <v>7.116014111111126</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7541313957931686</v>
+        <v>1.603673164296505</v>
       </c>
       <c r="F64" t="n">
-        <v>4.892182810459185</v>
+        <v>4.796082600153184</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0411077915787223</v>
+        <v>-0.1040361540683445</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2189499302340878</v>
+        <v>0.304680126152328</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5662,81 +5662,81 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.0930893630232769</v>
+        <v>0.2085389661966377</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1270494458008654</v>
+        <v>0.2253445997735045</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0912172230402596</v>
+        <v>0.4563006706910122</v>
       </c>
       <c r="M64" t="n">
-        <v>1.862389874674297</v>
+        <v>3.231576340957623</v>
       </c>
       <c r="N64" t="n">
-        <v>1.006242976651267</v>
+        <v>2.934780634026747</v>
       </c>
       <c r="O64" t="n">
-        <v>2.159342140738844</v>
+        <v>3.658690594881978</v>
       </c>
       <c r="P64" t="n">
-        <v>1.354934100171526</v>
+        <v>1.396682456629672</v>
       </c>
       <c r="Q64" t="n">
-        <v>8.605348638626504</v>
+        <v>6.787776750104146</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0025494912459698</v>
+        <v>0.0114603742749751</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>ADOM-SL8-1-2025</t>
+          <t>ADOM-SL9-1-2025</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>0.009204231830726699</v>
+        <v>0.0231416874332502</v>
       </c>
       <c r="V64" t="n">
-        <v>2.174</v>
+        <v>5.618</v>
       </c>
       <c r="W64" t="n">
-        <v>5.46</v>
+        <v>5.99</v>
       </c>
       <c r="X64" t="n">
-        <v>163</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ADOM-SL8-10-2025</t>
+          <t>ADOM-SL9-10-2025</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.619671254054245</v>
+        <v>26.25650299999993</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4976897499149946</v>
+        <v>8.241925222222203</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6438895733474338</v>
+        <v>0.7893017187837978</v>
       </c>
       <c r="F65" t="n">
-        <v>4.823935548687428</v>
+        <v>4.577463037891218</v>
       </c>
       <c r="G65" t="n">
-        <v>0.007076648533042</v>
+        <v>-0.08503965494270101</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0076367401032707</v>
+        <v>0.1990521680867933</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5744,81 +5744,81 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0.1250200387554153</v>
+        <v>0.3003002692915861</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1601695627310222</v>
+        <v>0.2815156770986922</v>
       </c>
       <c r="L65" t="n">
-        <v>0.1015553877051306</v>
+        <v>0.2180854078144034</v>
       </c>
       <c r="M65" t="n">
-        <v>5.076505649196209</v>
+        <v>3.147013029582898</v>
       </c>
       <c r="N65" t="n">
-        <v>4.350439173761966</v>
+        <v>2.57646562038146</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9399256374247488</v>
+        <v>3.222726241778328</v>
       </c>
       <c r="P65" t="n">
-        <v>1.297090227144994</v>
+        <v>1.356474941979659</v>
       </c>
       <c r="Q65" t="n">
-        <v>11.14209590634327</v>
+        <v>13.18347516755264</v>
       </c>
       <c r="R65" t="n">
-        <v>0.015368937548673</v>
+        <v>0.0103227215769997</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>ADOM-SL8-10-2025</t>
+          <t>ADOM-SL9-10-2025</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U65" t="n">
-        <v>0.0082536270194336</v>
+        <v>0.0255877616747181</v>
       </c>
       <c r="V65" t="n">
-        <v>1.801</v>
+        <v>5.589</v>
       </c>
       <c r="W65" t="n">
-        <v>5.72</v>
+        <v>6.56</v>
       </c>
       <c r="X65" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ADOM-SL8-2-2025</t>
+          <t>ADOM-SL9-11-2025</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.8509973462333144</v>
+        <v>25.33530300000007</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1611137742935035</v>
+        <v>7.320725222222241</v>
       </c>
       <c r="E66" t="n">
-        <v>1.063111030754908</v>
+        <v>0.7481806119565281</v>
       </c>
       <c r="F66" t="n">
-        <v>6.037221916079083</v>
+        <v>4.516459250895295</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0105368029706146</v>
+        <v>0.113605826171085</v>
       </c>
       <c r="H66" t="n">
-        <v>0.009597493717378501</v>
+        <v>0.0357404449289839</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5826,81 +5826,81 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.0310568930786714</v>
+        <v>0.3323500108632941</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0601142066719145</v>
+        <v>0.3163440779111925</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0703069956302507</v>
+        <v>0.2225146379009981</v>
       </c>
       <c r="M66" t="n">
-        <v>6.751163592335002</v>
+        <v>3.374348501935452</v>
       </c>
       <c r="N66" t="n">
-        <v>2.646946084394972</v>
+        <v>2.875712157068979</v>
       </c>
       <c r="O66" t="n">
-        <v>0.3626599896725765</v>
+        <v>4.211517165005417</v>
       </c>
       <c r="P66" t="n">
-        <v>1.352660993374422</v>
+        <v>1.331340113330054</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.407929084863714</v>
+        <v>15.07502535852535</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0132107527843126</v>
+        <v>0.0109973435509977</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>ADOM-SL8-2-2025</t>
+          <t>ADOM-SL9-11-2025</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U66" t="n">
-        <v>0.0059951924479463</v>
+        <v>0.0247041052070375</v>
       </c>
       <c r="V66" t="n">
-        <v>0.8693</v>
+        <v>5.627</v>
       </c>
       <c r="W66" t="n">
-        <v>4.88</v>
+        <v>6.65</v>
       </c>
       <c r="X66" t="n">
-        <v>167</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ADOM-SL8-3-2025</t>
+          <t>ADOM-SL9-12-2025</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.029805233086711</v>
+        <v>25.56560299999997</v>
       </c>
       <c r="D67" t="n">
-        <v>0.5125725834405427</v>
+        <v>8.548991888888837</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9374432848247364</v>
+        <v>0.8904461100629538</v>
       </c>
       <c r="F67" t="n">
-        <v>4.796521296056344</v>
+        <v>4.708400373568582</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0018767568379014</v>
+        <v>-0.1280442788598215</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0134510802969234</v>
+        <v>0.1743756372054816</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5908,81 +5908,81 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.0255378122637966</v>
+        <v>0.2757055271756719</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0500010978284005</v>
+        <v>0.2414356895777341</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0442469103383955</v>
+        <v>0.2180078960224756</v>
       </c>
       <c r="M67" t="n">
-        <v>2.173641521440373</v>
+        <v>2.960062090557521</v>
       </c>
       <c r="N67" t="n">
-        <v>1.591618890803203</v>
+        <v>2.601752344445227</v>
       </c>
       <c r="O67" t="n">
-        <v>2.015157763195704</v>
+        <v>3.644050885507784</v>
       </c>
       <c r="P67" t="n">
-        <v>1.297026801590305</v>
+        <v>1.389339794219597</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.159871697629353</v>
+        <v>11.95309708900873</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0056430109952637</v>
+        <v>0.0101653204727578</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>ADOM-SL8-3-2025</t>
+          <t>ADOM-SL9-12-2025</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U67" t="n">
-        <v>0.007655058491288</v>
+        <v>0.0294819962097283</v>
       </c>
       <c r="V67" t="n">
-        <v>0.6715</v>
+        <v>4.749</v>
       </c>
       <c r="W67" t="n">
-        <v>5.26</v>
+        <v>6.79</v>
       </c>
       <c r="X67" t="n">
-        <v>170</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ADOM-SL8-4-2025</t>
+          <t>ADOM-SL9-13-2025</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.5379092345048317</v>
+        <v>34.08670300000002</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1421514387178644</v>
+        <v>11.00552522222221</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8483626099853878</v>
+        <v>1.017764760429855</v>
       </c>
       <c r="F68" t="n">
-        <v>5.602425352635046</v>
+        <v>5.237272110299401</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0081231822223261</v>
+        <v>0.0181540229900321</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0053947084837035</v>
+        <v>0.3074963782134849</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5990,81 +5990,81 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0.0289441985753136</v>
+        <v>0.2549514538838975</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0566835989911642</v>
+        <v>0.2098768725670081</v>
       </c>
       <c r="L68" t="n">
-        <v>0.0485685421485773</v>
+        <v>0.2237614138857671</v>
       </c>
       <c r="M68" t="n">
-        <v>4.47684453156095</v>
+        <v>2.916158142678256</v>
       </c>
       <c r="N68" t="n">
-        <v>3.734853144278483</v>
+        <v>2.975279436986239</v>
       </c>
       <c r="O68" t="n">
-        <v>0.3627030515090207</v>
+        <v>4.818751781134331</v>
       </c>
       <c r="P68" t="n">
-        <v>1.311269885684133</v>
+        <v>1.440008711580939</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.186724730301997</v>
+        <v>11.23029036866052</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0152019640593978</v>
+        <v>0.0114480906004632</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>ADOM-SL8-4-2025</t>
+          <t>ADOM-SL9-13-2025</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U68" t="n">
-        <v>0.0033271073511315</v>
+        <v>0.0347161488300728</v>
       </c>
       <c r="V68" t="n">
-        <v>0.9102</v>
+        <v>5.214</v>
       </c>
       <c r="W68" t="n">
-        <v>4.64</v>
+        <v>6.1</v>
       </c>
       <c r="X68" t="n">
-        <v>246</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ADOM-SL8-6-2025</t>
+          <t>ADOM-SL9-3-2025</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>14.61355855555555</v>
+        <v>26.25650299999993</v>
       </c>
       <c r="D69" t="n">
-        <v>4.915369666666647</v>
+        <v>7.730147444444446</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9735133408022376</v>
+        <v>0.9763520161615574</v>
       </c>
       <c r="F69" t="n">
-        <v>4.844279740040788</v>
+        <v>4.85346105779481</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.07644549938132519</v>
+        <v>0.0615867977782258</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.2685540308984633</v>
+        <v>0.2602027529941253</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -6072,81 +6072,81 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0.250588190260506</v>
+        <v>0.2332360981518333</v>
       </c>
       <c r="K69" t="n">
-        <v>0.2432260452980393</v>
+        <v>0.2028594066211463</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2258117677198498</v>
+        <v>0.2041975837173477</v>
       </c>
       <c r="M69" t="n">
-        <v>3.02731240320993</v>
+        <v>3.201125766613463</v>
       </c>
       <c r="N69" t="n">
-        <v>1.819882141942098</v>
+        <v>3.24361885729859</v>
       </c>
       <c r="O69" t="n">
-        <v>2.337592333799219</v>
+        <v>3.541009971052083</v>
       </c>
       <c r="P69" t="n">
-        <v>1.34743041595129</v>
+        <v>1.380640604984215</v>
       </c>
       <c r="Q69" t="n">
-        <v>10.09725649926196</v>
+        <v>11.48266581414921</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0053543867896986</v>
+        <v>0.0127743454482729</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>ADOM-SL8-6-2025</t>
+          <t>ADOM-SL9-3-2025</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>0.0134568106312292</v>
+        <v>0.0271643228664997</v>
       </c>
       <c r="V69" t="n">
-        <v>6.02</v>
+        <v>5.191</v>
       </c>
       <c r="W69" t="n">
-        <v>6.19</v>
+        <v>7.1</v>
       </c>
       <c r="X69" t="n">
-        <v>-78</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ADOM-SL8-7-2025</t>
+          <t>ADOM-SL9-4-2025</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.221690300604591</v>
+        <v>26.94740300000002</v>
       </c>
       <c r="D70" t="n">
-        <v>0.363063221355901</v>
+        <v>8.088391888888944</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8940074095612393</v>
+        <v>1.017764760429855</v>
       </c>
       <c r="F70" t="n">
-        <v>4.666500811403682</v>
+        <v>5.237272110299401</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.011923834251994</v>
+        <v>-0.1730817019482629</v>
       </c>
       <c r="H70" t="n">
-        <v>0.009895199343366299</v>
+        <v>0.2816474760985201</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6154,81 +6154,81 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0.0453986503499962</v>
+        <v>0.2549514538838975</v>
       </c>
       <c r="K70" t="n">
-        <v>0.06615831058224619</v>
+        <v>0.2098768725670081</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0565662681756886</v>
+        <v>0.2237614138857671</v>
       </c>
       <c r="M70" t="n">
-        <v>3.753665951214149</v>
+        <v>3.136213782197314</v>
       </c>
       <c r="N70" t="n">
-        <v>2.109649724019844</v>
+        <v>3.328486038005145</v>
       </c>
       <c r="O70" t="n">
-        <v>1.210784133448859</v>
+        <v>3.492988469928098</v>
       </c>
       <c r="P70" t="n">
-        <v>1.291619654729089</v>
+        <v>1.440008711580939</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.299435842792887</v>
+        <v>11.23029036866052</v>
       </c>
       <c r="R70" t="n">
-        <v>0.008172062984486399</v>
+        <v>0.0131447831216748</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>ADOM-SL8-7-2025</t>
+          <t>ADOM-SL9-4-2025</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U70" t="n">
-        <v>0.0079942472624689</v>
+        <v>0.0306550493386521</v>
       </c>
       <c r="V70" t="n">
-        <v>0.8862</v>
+        <v>4.763</v>
       </c>
       <c r="W70" t="n">
-        <v>5.17</v>
+        <v>6.98</v>
       </c>
       <c r="X70" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ADOM-SL8-8-2025</t>
+          <t>ADOM-SL9-5-2025</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.299365837733731</v>
+        <v>32.93520299999999</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3990275164083509</v>
+        <v>10.62169188888892</v>
       </c>
       <c r="E71" t="n">
-        <v>0.6378196064404381</v>
+        <v>1.059844734721643</v>
       </c>
       <c r="F71" t="n">
-        <v>4.234446991444361</v>
+        <v>5.11655999414806</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0103435934676737</v>
+        <v>-0.144965767974142</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.0057786765345461</v>
+        <v>0.1954033200812137</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6236,81 +6236,81 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.07358473802961191</v>
+        <v>0.2595021015000975</v>
       </c>
       <c r="K71" t="n">
-        <v>0.09353426753557249</v>
+        <v>0.2222181262520525</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0593824578545125</v>
+        <v>0.2411211425823762</v>
       </c>
       <c r="M71" t="n">
-        <v>3.396979162382732</v>
+        <v>2.865785150783829</v>
       </c>
       <c r="N71" t="n">
-        <v>1.623952008437779</v>
+        <v>3.200012979427592</v>
       </c>
       <c r="O71" t="n">
-        <v>1.385932744734903</v>
+        <v>4.520093869169682</v>
       </c>
       <c r="P71" t="n">
-        <v>1.316063727879344</v>
+        <v>1.441570258676719</v>
       </c>
       <c r="Q71" t="n">
-        <v>9.049820755235608</v>
+        <v>8.090166608857801</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0052048230527531</v>
+        <v>0.0124805122538905</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>ADOM-SL8-8-2025</t>
+          <t>ADOM-SL9-5-2025</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>0.0054902855177584</v>
+        <v>0.0379713603818615</v>
       </c>
       <c r="V71" t="n">
-        <v>1.267</v>
+        <v>4.609</v>
       </c>
       <c r="W71" t="n">
-        <v>8.51</v>
+        <v>7.02</v>
       </c>
       <c r="X71" t="n">
-        <v>-17</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ADOM-SL8-9-2025</t>
+          <t>ADOM-SL9-7-2025</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.434114285857987</v>
+        <v>40.76540300000006</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3153154348315682</v>
+        <v>12.56644744444455</v>
       </c>
       <c r="E72" t="n">
-        <v>0.6946630411964939</v>
+        <v>0.8555497635245372</v>
       </c>
       <c r="F72" t="n">
-        <v>5.901128237630664</v>
+        <v>4.533103547326586</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0106036184597747</v>
+        <v>0.0219842556247549</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0008798269469297</v>
+        <v>0.2555275857383901</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6318,81 +6318,81 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.0881213652832526</v>
+        <v>0.3370904153865651</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1081319400160554</v>
+        <v>0.31693314803395</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0771155575409429</v>
+        <v>0.2592937858772864</v>
       </c>
       <c r="M72" t="n">
-        <v>4.589734136364382</v>
+        <v>3.020236607372143</v>
       </c>
       <c r="N72" t="n">
-        <v>3.177457496044924</v>
+        <v>3.335941515791863</v>
       </c>
       <c r="O72" t="n">
-        <v>0.7492257329201866</v>
+        <v>4.596744552375826</v>
       </c>
       <c r="P72" t="n">
-        <v>1.408495446610438</v>
+        <v>1.360911436935257</v>
       </c>
       <c r="Q72" t="n">
-        <v>9.74793182865031</v>
+        <v>12.25142436865928</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0131225155121707</v>
+        <v>0.012739537409201</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>ADOM-SL8-9-2025</t>
+          <t>ADOM-SL9-7-2025</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Storage 8</t>
+          <t>Storage 9</t>
         </is>
       </c>
       <c r="U72" t="n">
-        <v>0.0029247853607571</v>
+        <v>0.0385309641097818</v>
       </c>
       <c r="V72" t="n">
-        <v>2.747</v>
+        <v>5.684</v>
       </c>
       <c r="W72" t="n">
-        <v>4.79</v>
+        <v>7.11</v>
       </c>
       <c r="X72" t="n">
-        <v>189</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ADOM-SL9-1-2025</t>
+          <t>ADOM-SL9-8-2025</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>23.72320299999995</v>
+        <v>33.62610299999997</v>
       </c>
       <c r="D73" t="n">
-        <v>7.116014111111126</v>
+        <v>10.90316966666665</v>
       </c>
       <c r="E73" t="n">
-        <v>1.603673164296505</v>
+        <v>0.8032428312358257</v>
       </c>
       <c r="F73" t="n">
-        <v>4.796082600153184</v>
+        <v>4.950832974378061</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.1040361540683445</v>
+        <v>0.0207805045512934</v>
       </c>
       <c r="H73" t="n">
-        <v>0.304680126152328</v>
+        <v>0.3170122025766666</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6400,35 +6400,35 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.2085389661966377</v>
+        <v>0.4145689196800048</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2253445997735045</v>
+        <v>0.3407989123339653</v>
       </c>
       <c r="L73" t="n">
-        <v>0.4563006706910122</v>
+        <v>0.2502841988091951</v>
       </c>
       <c r="M73" t="n">
-        <v>3.231576340957623</v>
+        <v>2.939164264548782</v>
       </c>
       <c r="N73" t="n">
-        <v>2.934780634026747</v>
+        <v>2.801343949404278</v>
       </c>
       <c r="O73" t="n">
-        <v>3.658690594881978</v>
+        <v>4.01655704241345</v>
       </c>
       <c r="P73" t="n">
-        <v>1.396682456629672</v>
+        <v>1.392839734477152</v>
       </c>
       <c r="Q73" t="n">
-        <v>6.787776750104146</v>
+        <v>14.35716449390682</v>
       </c>
       <c r="R73" t="n">
-        <v>0.0114603742749751</v>
+        <v>0.0108506991487748</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>ADOM-SL9-1-2025</t>
+          <t>ADOM-SL9-8-2025</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -6437,44 +6437,44 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>0.0231416874332502</v>
+        <v>0.0295478289258896</v>
       </c>
       <c r="V73" t="n">
-        <v>5.618</v>
+        <v>6.126</v>
       </c>
       <c r="W73" t="n">
-        <v>5.99</v>
+        <v>5.6</v>
       </c>
       <c r="X73" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ADOM-SL9-10-2025</t>
+          <t>ADOM-SL9-9-2025</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>26.25650299999993</v>
+        <v>36.0058696666667</v>
       </c>
       <c r="D74" t="n">
-        <v>8.241925222222203</v>
+        <v>11.56848077777783</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7893017187837978</v>
+        <v>0.7003586032975497</v>
       </c>
       <c r="F74" t="n">
-        <v>4.577463037891218</v>
+        <v>4.366674958523455</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.08503965494270101</v>
+        <v>-0.1000100442449642</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1990521680867933</v>
+        <v>0.1969770893603168</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6482,35 +6482,35 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.3003002692915861</v>
+        <v>0.3895006712384356</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2815156770986922</v>
+        <v>0.3736311848160213</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2180854078144034</v>
+        <v>0.2351919588599153</v>
       </c>
       <c r="M74" t="n">
-        <v>3.147013029582898</v>
+        <v>2.982550514170568</v>
       </c>
       <c r="N74" t="n">
-        <v>2.57646562038146</v>
+        <v>2.811962157250544</v>
       </c>
       <c r="O74" t="n">
-        <v>3.222726241778328</v>
+        <v>4.059231937513587</v>
       </c>
       <c r="P74" t="n">
-        <v>1.356474941979659</v>
+        <v>1.320284167554231</v>
       </c>
       <c r="Q74" t="n">
-        <v>13.18347516755264</v>
+        <v>15.31088443045346</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0103227215769997</v>
+        <v>0.0108593807483691</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>ADOM-SL9-10-2025</t>
+          <t>ADOM-SL9-9-2025</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -6519,13 +6519,13 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>0.0255877616747181</v>
+        <v>0.0338912061174835</v>
       </c>
       <c r="V74" t="n">
-        <v>5.589</v>
+        <v>5.754</v>
       </c>
       <c r="W74" t="n">
-        <v>6.56</v>
+        <v>5.9</v>
       </c>
       <c r="X74" t="n">
         <v>42</v>
@@ -6533,768 +6533,768 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ADOM-SL9-11-2025</t>
+          <t>ADOM-SLB-B1-1-2025</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>25.33530300000007</v>
+        <v>4.992136333333278</v>
       </c>
       <c r="D75" t="n">
-        <v>7.320725222222241</v>
+        <v>2.023825222222134</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7481806119565281</v>
+        <v>0.6644011536237158</v>
       </c>
       <c r="F75" t="n">
-        <v>4.516459250895295</v>
+        <v>4.830380338052482</v>
       </c>
       <c r="G75" t="n">
-        <v>0.113605826171085</v>
+        <v>-0.0381263063536581</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0357404449289839</v>
+        <v>0.0064321552758443</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0.3323500108632941</v>
+        <v>0.06924042342008389</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3163440779111925</v>
+        <v>0.0951832753269642</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2225146379009981</v>
+        <v>0.0517844459478906</v>
       </c>
       <c r="M75" t="n">
-        <v>3.374348501935452</v>
+        <v>2.632354732610656</v>
       </c>
       <c r="N75" t="n">
-        <v>2.875712157068979</v>
+        <v>1.51765575892036</v>
       </c>
       <c r="O75" t="n">
-        <v>4.211517165005417</v>
+        <v>1.148651518369086</v>
       </c>
       <c r="P75" t="n">
-        <v>1.331340113330054</v>
+        <v>1.46079463819411</v>
       </c>
       <c r="Q75" t="n">
-        <v>15.07502535852535</v>
+        <v>14.82028529958319</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0109973435509977</v>
+        <v>0.0046273768122818</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>ADOM-SL9-11-2025</t>
+          <t>ADOM-SLB-B1-1-2025</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U75" t="n">
-        <v>0.0247041052070375</v>
+        <v>0.0207250996015936</v>
       </c>
       <c r="V75" t="n">
-        <v>5.627</v>
+        <v>1.255</v>
       </c>
       <c r="W75" t="n">
-        <v>6.65</v>
+        <v>7.4</v>
       </c>
       <c r="X75" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ADOM-SL9-12-2025</t>
+          <t>ADOM-SLB-B1-2-2025</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>25.56560299999997</v>
+        <v>2.705281737691027</v>
       </c>
       <c r="D76" t="n">
-        <v>8.548991888888837</v>
+        <v>0.7730873778347143</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8904461100629538</v>
+        <v>0.5840181613855107</v>
       </c>
       <c r="F76" t="n">
-        <v>4.708400373568582</v>
+        <v>4.516755642387482</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.1280442788598215</v>
+        <v>-0.0224184809613203</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1743756372054816</v>
+        <v>0.0143051088538951</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.2757055271756719</v>
+        <v>0.0598388599061929</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2414356895777341</v>
+        <v>0.08687248838960709</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2180078960224756</v>
+        <v>0.0460364422422283</v>
       </c>
       <c r="M76" t="n">
-        <v>2.960062090557521</v>
+        <v>3.271960250176574</v>
       </c>
       <c r="N76" t="n">
-        <v>2.601752344445227</v>
+        <v>3.714601899392315</v>
       </c>
       <c r="O76" t="n">
-        <v>3.644050885507784</v>
+        <v>2.473794811361025</v>
       </c>
       <c r="P76" t="n">
-        <v>1.389339794219597</v>
+        <v>1.328727531643786</v>
       </c>
       <c r="Q76" t="n">
-        <v>11.95309708900873</v>
+        <v>19.59949608097065</v>
       </c>
       <c r="R76" t="n">
-        <v>0.0101653204727578</v>
+        <v>0.0137629546628425</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>ADOM-SL9-12-2025</t>
+          <t>ADOM-SLB-B1-2-2025</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U76" t="n">
-        <v>0.0294819962097283</v>
+        <v>0.0127581347005895</v>
       </c>
       <c r="V76" t="n">
-        <v>4.749</v>
+        <v>0.9669</v>
       </c>
       <c r="W76" t="n">
-        <v>6.79</v>
+        <v>7.6</v>
       </c>
       <c r="X76" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ADOM-SL9-13-2025</t>
+          <t>ADOM-SLB-B1-3-2025</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>34.08670300000002</v>
+        <v>1.135373687969481</v>
       </c>
       <c r="D77" t="n">
-        <v>11.00552522222221</v>
+        <v>0.3634070144206759</v>
       </c>
       <c r="E77" t="n">
-        <v>1.017764760429855</v>
+        <v>0.755001546466891</v>
       </c>
       <c r="F77" t="n">
-        <v>5.237272110299401</v>
+        <v>4.169202316180781</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0181540229900321</v>
+        <v>-0.0211618350502955</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3074963782134849</v>
+        <v>0.0164100666170259</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.2549514538838975</v>
+        <v>0.0208271795040416</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2098768725670081</v>
+        <v>0.0509423906060261</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2237614138857671</v>
+        <v>0.0339231670722419</v>
       </c>
       <c r="M77" t="n">
-        <v>2.916158142678256</v>
+        <v>3.185832710901545</v>
       </c>
       <c r="N77" t="n">
-        <v>2.975279436986239</v>
+        <v>2.635416169541287</v>
       </c>
       <c r="O77" t="n">
-        <v>4.818751781134331</v>
+        <v>0.6932723403976918</v>
       </c>
       <c r="P77" t="n">
-        <v>1.440008711580939</v>
+        <v>1.381710892580438</v>
       </c>
       <c r="Q77" t="n">
-        <v>11.23029036866052</v>
+        <v>12.40874117970035</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0114480906004632</v>
+        <v>0.0115483674248826</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>ADOM-SL9-13-2025</t>
+          <t>ADOM-SLB-B1-3-2025</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U77" t="n">
-        <v>0.0347161488300728</v>
+        <v>0.0029907487316176</v>
       </c>
       <c r="V77" t="n">
-        <v>5.214</v>
+        <v>1.36</v>
       </c>
       <c r="W77" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="X77" t="n">
-        <v>69</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ADOM-SL9-3-2025</t>
+          <t>ADOM-SLB-B1-5-2025</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>26.25650299999993</v>
+        <v>2.212057768091977</v>
       </c>
       <c r="D78" t="n">
-        <v>7.730147444444446</v>
+        <v>0.5561780354167898</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9763520161615574</v>
+        <v>0.5681358336498401</v>
       </c>
       <c r="F78" t="n">
-        <v>4.85346105779481</v>
+        <v>4.463478567508632</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0615867977782258</v>
+        <v>-0.0124766357906003</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2602027529941253</v>
+        <v>0.0247875642970608</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.2332360981518333</v>
+        <v>0.06256298154716031</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2028594066211463</v>
+        <v>0.0958305414727689</v>
       </c>
       <c r="L78" t="n">
-        <v>0.2041975837173477</v>
+        <v>0.0488646324024988</v>
       </c>
       <c r="M78" t="n">
-        <v>3.201125766613463</v>
+        <v>3.903136613933175</v>
       </c>
       <c r="N78" t="n">
-        <v>3.24361885729859</v>
+        <v>3.665515364691021</v>
       </c>
       <c r="O78" t="n">
-        <v>3.541009971052083</v>
+        <v>1.010095059484576</v>
       </c>
       <c r="P78" t="n">
-        <v>1.380640604984215</v>
+        <v>1.396209930591571</v>
       </c>
       <c r="Q78" t="n">
-        <v>11.48266581414921</v>
+        <v>18.0190050696615</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0127743454482729</v>
+        <v>0.0146129521350927</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>ADOM-SL9-3-2025</t>
+          <t>ADOM-SLB-B1-5-2025</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U78" t="n">
-        <v>0.0271643228664997</v>
+        <v>0.0106508209149789</v>
       </c>
       <c r="V78" t="n">
-        <v>5.191</v>
+        <v>0.948</v>
       </c>
       <c r="W78" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="X78" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ADOM-SL9-4-2025</t>
+          <t>ADOM-SLB-B1-6-2025</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>26.94740300000002</v>
+        <v>3.147509652697873</v>
       </c>
       <c r="D79" t="n">
-        <v>8.088391888888944</v>
+        <v>0.5890905354934122</v>
       </c>
       <c r="E79" t="n">
-        <v>1.017764760429855</v>
+        <v>0.7260330416118591</v>
       </c>
       <c r="F79" t="n">
-        <v>5.237272110299401</v>
+        <v>4.540485750646977</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.1730817019482629</v>
+        <v>-0.0994527740134931</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2816474760985201</v>
+        <v>0.0318466714494967</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.2549514538838975</v>
+        <v>0.0715967368115405</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2098768725670081</v>
+        <v>0.1035623886791977</v>
       </c>
       <c r="L79" t="n">
-        <v>0.2237614138857671</v>
+        <v>0.0711617907462687</v>
       </c>
       <c r="M79" t="n">
-        <v>3.136213782197314</v>
+        <v>4.963546536248648</v>
       </c>
       <c r="N79" t="n">
-        <v>3.328486038005145</v>
+        <v>3.192636177731002</v>
       </c>
       <c r="O79" t="n">
-        <v>3.492988469928098</v>
+        <v>1.748050336291731</v>
       </c>
       <c r="P79" t="n">
-        <v>1.440008711580939</v>
+        <v>1.44174373616483</v>
       </c>
       <c r="Q79" t="n">
-        <v>11.23029036866052</v>
+        <v>14.19469390848171</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0131447831216748</v>
+        <v>0.012010656255703</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>ADOM-SL9-4-2025</t>
+          <t>ADOM-SLB-B1-6-2025</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U79" t="n">
-        <v>0.0306550493386521</v>
+        <v>0.0081565782785915</v>
       </c>
       <c r="V79" t="n">
-        <v>4.763</v>
+        <v>1.761</v>
       </c>
       <c r="W79" t="n">
-        <v>6.98</v>
+        <v>7.89</v>
       </c>
       <c r="X79" t="n">
-        <v>143</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ADOM-SL9-5-2025</t>
+          <t>ADOM-SLB-B1-7-2025</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>32.93520299999999</v>
+        <v>2.78508547711426</v>
       </c>
       <c r="D80" t="n">
-        <v>10.62169188888892</v>
+        <v>0.5934024434231056</v>
       </c>
       <c r="E80" t="n">
-        <v>1.059844734721643</v>
+        <v>0.9088508362693341</v>
       </c>
       <c r="F80" t="n">
-        <v>5.11655999414806</v>
+        <v>4.417372801351197</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.144965767974142</v>
+        <v>-0.01622534905409</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1954033200812137</v>
+        <v>0.0081267446909499</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0.2595021015000975</v>
+        <v>0.0667542996740885</v>
       </c>
       <c r="K80" t="n">
-        <v>0.2222181262520525</v>
+        <v>0.09755709531223331</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2411211425823762</v>
+        <v>0.0843721804913503</v>
       </c>
       <c r="M80" t="n">
-        <v>2.865785150783829</v>
+        <v>4.730240402096238</v>
       </c>
       <c r="N80" t="n">
-        <v>3.200012979427592</v>
+        <v>3.438024645508051</v>
       </c>
       <c r="O80" t="n">
-        <v>4.520093869169682</v>
+        <v>1.30948176859396</v>
       </c>
       <c r="P80" t="n">
-        <v>1.441570258676719</v>
+        <v>1.291543404424456</v>
       </c>
       <c r="Q80" t="n">
-        <v>8.090166608857801</v>
+        <v>6.959643861347394</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0124805122538905</v>
+        <v>0.0136767085092818</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>ADOM-SL9-5-2025</t>
+          <t>ADOM-SLB-B1-7-2025</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U80" t="n">
-        <v>0.0379713603818615</v>
+        <v>0.0159540045720789</v>
       </c>
       <c r="V80" t="n">
-        <v>4.609</v>
+        <v>0.9442969</v>
       </c>
       <c r="W80" t="n">
-        <v>7.02</v>
+        <v>7.9</v>
       </c>
       <c r="X80" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ADOM-SL9-7-2025</t>
+          <t>ADOM-SLB-B1-8-2025</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>40.76540300000006</v>
+        <v>3.460466675979087</v>
       </c>
       <c r="D81" t="n">
-        <v>12.56644744444455</v>
+        <v>0.9486631571636334</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8555497635245372</v>
+        <v>0.6135681192435226</v>
       </c>
       <c r="F81" t="n">
-        <v>4.533103547326586</v>
+        <v>4.278948776078064</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0219842556247549</v>
+        <v>-0.0414848094701811</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2555275857383901</v>
+        <v>0.0204970389631672</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.3370904153865651</v>
+        <v>0.0503427122558302</v>
       </c>
       <c r="K81" t="n">
-        <v>0.31693314803395</v>
+        <v>0.08165227155081339</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2592937858772864</v>
+        <v>0.0482547480568968</v>
       </c>
       <c r="M81" t="n">
-        <v>3.020236607372143</v>
+        <v>3.268252991107606</v>
       </c>
       <c r="N81" t="n">
-        <v>3.335941515791863</v>
+        <v>4.911277936186309</v>
       </c>
       <c r="O81" t="n">
-        <v>4.596744552375826</v>
+        <v>1.768339550762899</v>
       </c>
       <c r="P81" t="n">
-        <v>1.360911436935257</v>
+        <v>1.307785944249897</v>
       </c>
       <c r="Q81" t="n">
-        <v>12.25142436865928</v>
+        <v>14.44873979781245</v>
       </c>
       <c r="R81" t="n">
-        <v>0.012739537409201</v>
+        <v>0.0168903852673798</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>ADOM-SL9-7-2025</t>
+          <t>ADOM-SLB-B1-8-2025</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U81" t="n">
-        <v>0.0385309641097818</v>
+        <v>0.0072891696375111</v>
       </c>
       <c r="V81" t="n">
-        <v>5.684</v>
+        <v>2.218</v>
       </c>
       <c r="W81" t="n">
-        <v>7.11</v>
+        <v>7.76</v>
       </c>
       <c r="X81" t="n">
-        <v>125</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ADOM-SL9-8-2025</t>
+          <t>ADOM-SLB-B2-1-2025</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>33.62610299999997</v>
+        <v>5.187905690296342</v>
       </c>
       <c r="D82" t="n">
-        <v>10.90316966666665</v>
+        <v>1.593455944831536</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8032428312358257</v>
+        <v>1.218816995498371</v>
       </c>
       <c r="F82" t="n">
-        <v>4.950832974378061</v>
+        <v>4.99201853316977</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0207805045512934</v>
+        <v>-0.0609698423808882</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3170122025766666</v>
+        <v>0.06336732031485789</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>0.4145689196800048</v>
+        <v>0.08015918993714891</v>
       </c>
       <c r="K82" t="n">
-        <v>0.3407989123339653</v>
+        <v>0.1183474084414164</v>
       </c>
       <c r="L82" t="n">
-        <v>0.2502841988091951</v>
+        <v>0.1292842418990987</v>
       </c>
       <c r="M82" t="n">
-        <v>2.939164264548782</v>
+        <v>3.171393195282256</v>
       </c>
       <c r="N82" t="n">
-        <v>2.801343949404278</v>
+        <v>4.676330401583584</v>
       </c>
       <c r="O82" t="n">
-        <v>4.01655704241345</v>
+        <v>4.549324962402821</v>
       </c>
       <c r="P82" t="n">
-        <v>1.392839734477152</v>
+        <v>1.586466678886047</v>
       </c>
       <c r="Q82" t="n">
-        <v>14.35716449390682</v>
+        <v>7.105682355881095</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0108506991487748</v>
+        <v>0.0167735153509429</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>ADOM-SL9-8-2025</t>
+          <t>ADOM-SLB-B2-1-2025</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U82" t="n">
-        <v>0.0295478289258896</v>
+        <v>0.0144267021665793</v>
       </c>
       <c r="V82" t="n">
-        <v>6.126</v>
+        <v>1.909</v>
       </c>
       <c r="W82" t="n">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="X82" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ADOM-SL9-9-2025</t>
+          <t>ADOM-SLB-B2-3-2025</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>36.0058696666667</v>
+        <v>3.586947583610817</v>
       </c>
       <c r="D83" t="n">
-        <v>11.56848077777783</v>
+        <v>0.6532684788242754</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7003586032975497</v>
+        <v>1.400427031157082</v>
       </c>
       <c r="F83" t="n">
-        <v>4.366674958523455</v>
+        <v>4.423473530530813</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.1000100442449642</v>
+        <v>-0.0554715178713278</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1969770893603168</v>
+        <v>0.0019765992558573</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ADOM</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>0.3895006712384356</v>
+        <v>0.0577811553559578</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3736311848160213</v>
+        <v>0.1106180703836583</v>
       </c>
       <c r="L83" t="n">
-        <v>0.2351919588599153</v>
+        <v>0.1661325002046458</v>
       </c>
       <c r="M83" t="n">
-        <v>2.982550514170568</v>
+        <v>5.758581639861432</v>
       </c>
       <c r="N83" t="n">
-        <v>2.811962157250544</v>
+        <v>3.579201725940764</v>
       </c>
       <c r="O83" t="n">
-        <v>4.059231937513587</v>
+        <v>2.037412840220555</v>
       </c>
       <c r="P83" t="n">
-        <v>1.320284167554231</v>
+        <v>1.452412788294814</v>
       </c>
       <c r="Q83" t="n">
-        <v>15.31088443045346</v>
+        <v>4.867909763808245</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0108593807483691</v>
+        <v>0.0129358835310071</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>ADOM-SL9-9-2025</t>
+          <t>ADOM-SLB-B2-3-2025</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>Storage 9</t>
+          <t>Baikal</t>
         </is>
       </c>
       <c r="U83" t="n">
-        <v>0.0338912061174835</v>
+        <v>0.0045724458839424</v>
       </c>
       <c r="V83" t="n">
-        <v>5.754</v>
+        <v>4.241</v>
       </c>
       <c r="W83" t="n">
-        <v>5.9</v>
+        <v>7.56</v>
       </c>
       <c r="X83" t="n">
-        <v>42</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-1-2025</t>
+          <t>ADOM-SLB-B3-1-2025</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4.992136333333278</v>
+        <v>3.734281302735107</v>
       </c>
       <c r="D84" t="n">
-        <v>2.023825222222134</v>
+        <v>0.7651931046835306</v>
       </c>
       <c r="E84" t="n">
-        <v>0.6644011536237158</v>
+        <v>0.7192910839176968</v>
       </c>
       <c r="F84" t="n">
-        <v>4.830380338052482</v>
+        <v>4.675018822842357</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.0381263063536581</v>
+        <v>-0.041053612808283</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0064321552758443</v>
+        <v>0.0219019411559115</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7302,35 +7302,35 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>0.06924042342008389</v>
+        <v>0.1258561381778225</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0951832753269642</v>
+        <v>0.1477258430508749</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0517844459478906</v>
+        <v>0.1000797220583495</v>
       </c>
       <c r="M84" t="n">
-        <v>2.632354732610656</v>
+        <v>4.599423801931846</v>
       </c>
       <c r="N84" t="n">
-        <v>1.51765575892036</v>
+        <v>5.915505913234116</v>
       </c>
       <c r="O84" t="n">
-        <v>1.148651518369086</v>
+        <v>0.9080546740758026</v>
       </c>
       <c r="P84" t="n">
-        <v>1.46079463819411</v>
+        <v>1.450060728328301</v>
       </c>
       <c r="Q84" t="n">
-        <v>14.82028529958319</v>
+        <v>14.43393720942412</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0046273768122818</v>
+        <v>0.0190408639738073</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-1-2025</t>
+          <t>ADOM-SLB-B3-1-2025</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -7339,44 +7339,44 @@
         </is>
       </c>
       <c r="U84" t="n">
-        <v>0.0207250996015936</v>
+        <v>0.0064754245644885</v>
       </c>
       <c r="V84" t="n">
-        <v>1.255</v>
+        <v>2.923</v>
       </c>
       <c r="W84" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="X84" t="n">
-        <v>120</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-2-2025</t>
+          <t>ADOM-SLB-B3-3-2025</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2.705281737691027</v>
+        <v>2.270670351481648</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7730873778347143</v>
+        <v>0.43213660579314</v>
       </c>
       <c r="E85" t="n">
-        <v>0.5840181613855107</v>
+        <v>0.8879202039004209</v>
       </c>
       <c r="F85" t="n">
-        <v>4.516755642387482</v>
+        <v>5.659381915101706</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.0224184809613203</v>
+        <v>-0.0452566736670347</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0143051088538951</v>
+        <v>-0.0068644302589161</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7384,35 +7384,35 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>0.0598388599061929</v>
+        <v>0.1029305899458807</v>
       </c>
       <c r="K85" t="n">
-        <v>0.08687248838960709</v>
+        <v>0.1162779815461913</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0460364422422283</v>
+        <v>0.0970102524793984</v>
       </c>
       <c r="M85" t="n">
-        <v>3.271960250176574</v>
+        <v>5.412883507108889</v>
       </c>
       <c r="N85" t="n">
-        <v>3.714601899392315</v>
+        <v>3.88855344709407</v>
       </c>
       <c r="O85" t="n">
-        <v>2.473794811361025</v>
+        <v>0.6792283555587669</v>
       </c>
       <c r="P85" t="n">
-        <v>1.328727531643786</v>
+        <v>1.552392449176712</v>
       </c>
       <c r="Q85" t="n">
-        <v>19.59949608097065</v>
+        <v>11.61196852178568</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0137629546628425</v>
+        <v>0.0142915989217491</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-2-2025</t>
+          <t>ADOM-SLB-B3-3-2025</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -7421,44 +7421,44 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>0.0127581347005895</v>
+        <v>0.0057173843758252</v>
       </c>
       <c r="V85" t="n">
-        <v>0.9669</v>
+        <v>1.969</v>
       </c>
       <c r="W85" t="n">
         <v>7.6</v>
       </c>
       <c r="X85" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-3-2025</t>
+          <t>ADOM-SLB-BO-2-2025</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.135373687969481</v>
+        <v>3.303197714545863</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3634070144206759</v>
+        <v>0.5651954422584899</v>
       </c>
       <c r="E86" t="n">
-        <v>0.755001546466891</v>
+        <v>0.7196487377380401</v>
       </c>
       <c r="F86" t="n">
-        <v>4.169202316180781</v>
+        <v>5.273623749752255</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.0211618350502955</v>
+        <v>-0.103459571042332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0164100666170259</v>
+        <v>0.005507681709925</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -7466,35 +7466,35 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>0.0208271795040416</v>
+        <v>0.07453256902421609</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0509423906060261</v>
+        <v>0.0954314586728383</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0339231670722419</v>
+        <v>0.0557138528186474</v>
       </c>
       <c r="M86" t="n">
-        <v>3.185832710901545</v>
+        <v>5.368106440618767</v>
       </c>
       <c r="N86" t="n">
-        <v>2.635416169541287</v>
+        <v>3.441093551228285</v>
       </c>
       <c r="O86" t="n">
-        <v>0.6932723403976918</v>
+        <v>1.023942713154908</v>
       </c>
       <c r="P86" t="n">
-        <v>1.381710892580438</v>
+        <v>1.503102481814365</v>
       </c>
       <c r="Q86" t="n">
-        <v>12.40874117970035</v>
+        <v>10.88681148031653</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0115483674248826</v>
+        <v>0.0131309346155619</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-3-2025</t>
+          <t>ADOM-SLB-BO-2-2025</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -7503,44 +7503,44 @@
         </is>
       </c>
       <c r="U86" t="n">
-        <v>0.0029907487316176</v>
+        <v>0.0062332263022026</v>
       </c>
       <c r="V86" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="W86" t="n">
         <v>7.6</v>
       </c>
       <c r="X86" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-5-2025</t>
+          <t>ADOM-SLB-BO-3-2025</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.212057768091977</v>
+        <v>1.886736278549499</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5561780354167898</v>
+        <v>0.4929669868370014</v>
       </c>
       <c r="E87" t="n">
-        <v>0.5681358336498401</v>
+        <v>0.7145300163504961</v>
       </c>
       <c r="F87" t="n">
-        <v>4.463478567508632</v>
+        <v>4.594192242583246</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.0124766357906003</v>
+        <v>-0.0122935111840325</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0247875642970608</v>
+        <v>-0.0053647102965337</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -7548,35 +7548,35 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>0.06256298154716031</v>
+        <v>0.06818770650997941</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0958305414727689</v>
+        <v>0.0989040569959081</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0488646324024988</v>
+        <v>0.0603953540486235</v>
       </c>
       <c r="M87" t="n">
-        <v>3.903136613933175</v>
+        <v>3.846188236663951</v>
       </c>
       <c r="N87" t="n">
-        <v>3.665515364691021</v>
+        <v>3.458506779934782</v>
       </c>
       <c r="O87" t="n">
-        <v>1.010095059484576</v>
+        <v>0.7862592399162694</v>
       </c>
       <c r="P87" t="n">
-        <v>1.396209930591571</v>
+        <v>1.369018357404276</v>
       </c>
       <c r="Q87" t="n">
-        <v>18.0190050696615</v>
+        <v>13.51730418563341</v>
       </c>
       <c r="R87" t="n">
-        <v>0.0146129521350927</v>
+        <v>0.0135832945320816</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>ADOM-SLB-B1-5-2025</t>
+          <t>ADOM-SLB-BO-3-2025</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -7585,753 +7585,15 @@
         </is>
       </c>
       <c r="U87" t="n">
-        <v>0.0106508209149789</v>
+        <v>0.0047038642323869</v>
       </c>
       <c r="V87" t="n">
-        <v>0.948</v>
+        <v>1.902</v>
       </c>
       <c r="W87" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="X87" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>183</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-6-2025</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>3.147509652697873</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0.5890905354934122</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0.7260330416118591</v>
-      </c>
-      <c r="F88" t="n">
-        <v>4.540485750646977</v>
-      </c>
-      <c r="G88" t="n">
-        <v>-0.0994527740134931</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.0318466714494967</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>0.0715967368115405</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0.1035623886791977</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0.0711617907462687</v>
-      </c>
-      <c r="M88" t="n">
-        <v>4.963546536248648</v>
-      </c>
-      <c r="N88" t="n">
-        <v>3.192636177731002</v>
-      </c>
-      <c r="O88" t="n">
-        <v>1.748050336291731</v>
-      </c>
-      <c r="P88" t="n">
-        <v>1.44174373616483</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>14.19469390848171</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.012010656255703</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-6-2025</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>0.0081565782785915</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1.761</v>
-      </c>
-      <c r="W88" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="X88" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>184</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-7-2025</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>2.78508547711426</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.5934024434231056</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0.9088508362693341</v>
-      </c>
-      <c r="F89" t="n">
-        <v>4.417372801351197</v>
-      </c>
-      <c r="G89" t="n">
-        <v>-0.01622534905409</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0.0081267446909499</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>0.0667542996740885</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0.09755709531223331</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0.0843721804913503</v>
-      </c>
-      <c r="M89" t="n">
-        <v>4.730240402096238</v>
-      </c>
-      <c r="N89" t="n">
-        <v>3.438024645508051</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1.30948176859396</v>
-      </c>
-      <c r="P89" t="n">
-        <v>1.291543404424456</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>6.959643861347394</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0.0136767085092818</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-7-2025</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U89" t="n">
-        <v>0.0159540045720789</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0.9442969</v>
-      </c>
-      <c r="W89" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="X89" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>185</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-8-2025</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>3.460466675979087</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0.9486631571636334</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.6135681192435226</v>
-      </c>
-      <c r="F90" t="n">
-        <v>4.278948776078064</v>
-      </c>
-      <c r="G90" t="n">
-        <v>-0.0414848094701811</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0.0204970389631672</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>0.0503427122558302</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0.08165227155081339</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0.0482547480568968</v>
-      </c>
-      <c r="M90" t="n">
-        <v>3.268252991107606</v>
-      </c>
-      <c r="N90" t="n">
-        <v>4.911277936186309</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1.768339550762899</v>
-      </c>
-      <c r="P90" t="n">
-        <v>1.307785944249897</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>14.44873979781245</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0.0168903852673798</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B1-8-2025</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U90" t="n">
-        <v>0.0072891696375111</v>
-      </c>
-      <c r="V90" t="n">
-        <v>2.218</v>
-      </c>
-      <c r="W90" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="X90" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>186</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2-1-2025</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>5.187905690296342</v>
-      </c>
-      <c r="D91" t="n">
-        <v>1.593455944831536</v>
-      </c>
-      <c r="E91" t="n">
-        <v>1.218816995498371</v>
-      </c>
-      <c r="F91" t="n">
-        <v>4.99201853316977</v>
-      </c>
-      <c r="G91" t="n">
-        <v>-0.0609698423808882</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0.06336732031485789</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>0.08015918993714891</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0.1183474084414164</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0.1292842418990987</v>
-      </c>
-      <c r="M91" t="n">
-        <v>3.171393195282256</v>
-      </c>
-      <c r="N91" t="n">
-        <v>4.676330401583584</v>
-      </c>
-      <c r="O91" t="n">
-        <v>4.549324962402821</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1.586466678886047</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>7.105682355881095</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.0167735153509429</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2-1-2025</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U91" t="n">
-        <v>0.0144267021665793</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1.909</v>
-      </c>
-      <c r="W91" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="X91" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>187</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2-3-2025</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>3.586947583610817</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.6532684788242754</v>
-      </c>
-      <c r="E92" t="n">
-        <v>1.400427031157082</v>
-      </c>
-      <c r="F92" t="n">
-        <v>4.423473530530813</v>
-      </c>
-      <c r="G92" t="n">
-        <v>-0.0554715178713278</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.0019765992558573</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>0.0577811553559578</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0.1106180703836583</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0.1661325002046458</v>
-      </c>
-      <c r="M92" t="n">
-        <v>5.758581639861432</v>
-      </c>
-      <c r="N92" t="n">
-        <v>3.579201725940764</v>
-      </c>
-      <c r="O92" t="n">
-        <v>2.037412840220555</v>
-      </c>
-      <c r="P92" t="n">
-        <v>1.452412788294814</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>4.867909763808245</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.0129358835310071</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B2-3-2025</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U92" t="n">
-        <v>0.0045724458839424</v>
-      </c>
-      <c r="V92" t="n">
-        <v>4.241</v>
-      </c>
-      <c r="W92" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="X92" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>193</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B3-1-2025</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>3.734281302735107</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.7651931046835306</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0.7192910839176968</v>
-      </c>
-      <c r="F93" t="n">
-        <v>4.675018822842357</v>
-      </c>
-      <c r="G93" t="n">
-        <v>-0.041053612808283</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0.0219019411559115</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>0.1258561381778225</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0.1477258430508749</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0.1000797220583495</v>
-      </c>
-      <c r="M93" t="n">
-        <v>4.599423801931846</v>
-      </c>
-      <c r="N93" t="n">
-        <v>5.915505913234116</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0.9080546740758026</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1.450060728328301</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>14.43393720942412</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0.0190408639738073</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B3-1-2025</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U93" t="n">
-        <v>0.0064754245644885</v>
-      </c>
-      <c r="V93" t="n">
-        <v>2.923</v>
-      </c>
-      <c r="W93" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="X93" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>195</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B3-3-2025</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>2.270670351481648</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.43213660579314</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0.8879202039004209</v>
-      </c>
-      <c r="F94" t="n">
-        <v>5.659381915101706</v>
-      </c>
-      <c r="G94" t="n">
-        <v>-0.0452566736670347</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-0.0068644302589161</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>0.1029305899458807</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0.1162779815461913</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0.0970102524793984</v>
-      </c>
-      <c r="M94" t="n">
-        <v>5.412883507108889</v>
-      </c>
-      <c r="N94" t="n">
-        <v>3.88855344709407</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0.6792283555587669</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1.552392449176712</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>11.61196852178568</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0.0142915989217491</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-B3-3-2025</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U94" t="n">
-        <v>0.0057173843758252</v>
-      </c>
-      <c r="V94" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="W94" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="X94" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>196</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-BO-2-2025</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>3.303197714545863</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0.5651954422584899</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0.7196487377380401</v>
-      </c>
-      <c r="F95" t="n">
-        <v>5.273623749752255</v>
-      </c>
-      <c r="G95" t="n">
-        <v>-0.103459571042332</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.005507681709925</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>0.07453256902421609</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0.0954314586728383</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0.0557138528186474</v>
-      </c>
-      <c r="M95" t="n">
-        <v>5.368106440618767</v>
-      </c>
-      <c r="N95" t="n">
-        <v>3.441093551228285</v>
-      </c>
-      <c r="O95" t="n">
-        <v>1.023942713154908</v>
-      </c>
-      <c r="P95" t="n">
-        <v>1.503102481814365</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>10.88681148031653</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0.0131309346155619</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-BO-2-2025</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U95" t="n">
-        <v>0.0062332263022026</v>
-      </c>
-      <c r="V95" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="W95" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="X95" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>197</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-BO-3-2025</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>1.886736278549499</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.4929669868370014</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.7145300163504961</v>
-      </c>
-      <c r="F96" t="n">
-        <v>4.594192242583246</v>
-      </c>
-      <c r="G96" t="n">
-        <v>-0.0122935111840325</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-0.0053647102965337</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>0.06818770650997941</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0.0989040569959081</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0.0603953540486235</v>
-      </c>
-      <c r="M96" t="n">
-        <v>3.846188236663951</v>
-      </c>
-      <c r="N96" t="n">
-        <v>3.458506779934782</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0.7862592399162694</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1.369018357404276</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>13.51730418563341</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0.0135832945320816</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>ADOM-SLB-BO-3-2025</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Baikal</t>
-        </is>
-      </c>
-      <c r="U96" t="n">
-        <v>0.0047038642323869</v>
-      </c>
-      <c r="V96" t="n">
-        <v>1.902</v>
-      </c>
-      <c r="W96" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="X96" t="n">
         <v>24</v>
       </c>
     </row>
